--- a/filesystem/Finance/Financials/Thornfield_FY2025_standalone.xlsx
+++ b/filesystem/Finance/Financials/Thornfield_FY2025_standalone.xlsx
@@ -208,7 +208,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -386,11 +386,211 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="hair">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="hair">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002563EB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002563EB"/>
+      </right>
+      <top style="medium">
+        <color rgb="002563EB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002563EB"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002563EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002563EB"/>
+      </right>
+      <top style="medium">
+        <color rgb="002563EB"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002563EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="hair">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom style="hair">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <right/>
+      <top style="medium">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -523,6 +723,22 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -849,12 +1065,6 @@
           <t>THORNFIELD LIFE SCIENCES MARKETING — FY2025 Standalone Financials</t>
         </is>
       </c>
-      <c r="B1" s="16" t="n"/>
-      <c r="C1" s="16" t="n"/>
-      <c r="D1" s="16" t="n"/>
-      <c r="E1" s="16" t="n"/>
-      <c r="F1" s="16" t="n"/>
-      <c r="G1" s="16" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1"/>
     <row r="3" ht="22" customHeight="1">
@@ -863,16 +1073,16 @@
           <t>Entity:</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>Thornfield Life Sciences Marketing, Inc.</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n"/>
-      <c r="D3" s="18" t="n"/>
-      <c r="E3" s="18" t="n"/>
-      <c r="F3" s="18" t="n"/>
-      <c r="G3" s="19" t="n"/>
+      <c r="C3" s="47" t="n"/>
+      <c r="D3" s="47" t="n"/>
+      <c r="E3" s="47" t="n"/>
+      <c r="F3" s="47" t="n"/>
+      <c r="G3" s="48" t="n"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="20" t="inlineStr">
@@ -880,16 +1090,16 @@
           <t>Scope:</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Thornfield-native client accounts only. Excludes accounts inherited from Bramwell Scientific Marketing (post-close subsidiary). No CUST IDs in this workbook overlap with the Bramwell FY2025 Standalone.</t>
         </is>
       </c>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="21" t="n"/>
-      <c r="G4" s="22" t="n"/>
+      <c r="C4" s="49" t="n"/>
+      <c r="D4" s="49" t="n"/>
+      <c r="E4" s="49" t="n"/>
+      <c r="F4" s="49" t="n"/>
+      <c r="G4" s="50" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
@@ -897,16 +1107,16 @@
           <t>Fiscal year:</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>FY2025 (01/01/2025 – 12/31/2025)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="n"/>
-      <c r="D5" s="21" t="n"/>
-      <c r="E5" s="21" t="n"/>
-      <c r="F5" s="21" t="n"/>
-      <c r="G5" s="22" t="n"/>
+      <c r="C5" s="49" t="n"/>
+      <c r="D5" s="49" t="n"/>
+      <c r="E5" s="49" t="n"/>
+      <c r="F5" s="49" t="n"/>
+      <c r="G5" s="50" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
@@ -914,16 +1124,16 @@
           <t>Currency:</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="C6" s="21" t="n"/>
-      <c r="D6" s="21" t="n"/>
-      <c r="E6" s="21" t="n"/>
-      <c r="F6" s="21" t="n"/>
-      <c r="G6" s="22" t="n"/>
+      <c r="C6" s="49" t="n"/>
+      <c r="D6" s="49" t="n"/>
+      <c r="E6" s="49" t="n"/>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="50" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="20" t="inlineStr">
@@ -931,16 +1141,16 @@
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Ted Kowalczyk, VP Paid Media (owner of record)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="n"/>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="22" t="n"/>
+      <c r="C7" s="49" t="n"/>
+      <c r="D7" s="49" t="n"/>
+      <c r="E7" s="49" t="n"/>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="50" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
@@ -948,16 +1158,16 @@
           <t>Compiled by:</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Finance (A. Rutherford) — management sign-off on file</t>
         </is>
       </c>
-      <c r="C8" s="21" t="n"/>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="21" t="n"/>
-      <c r="F8" s="21" t="n"/>
-      <c r="G8" s="22" t="n"/>
+      <c r="C8" s="49" t="n"/>
+      <c r="D8" s="49" t="n"/>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="50" t="n"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="20" t="inlineStr">
@@ -965,16 +1175,16 @@
           <t>Status:</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Management-prepared; no external attestation performed. Figures are final for management-reporting purposes as of the FY2025 close.</t>
         </is>
       </c>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="21" t="n"/>
-      <c r="F9" s="21" t="n"/>
-      <c r="G9" s="22" t="n"/>
+      <c r="C9" s="49" t="n"/>
+      <c r="D9" s="49" t="n"/>
+      <c r="E9" s="49" t="n"/>
+      <c r="F9" s="49" t="n"/>
+      <c r="G9" s="50" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="20" t="inlineStr">
@@ -982,16 +1192,16 @@
           <t>ERPNext source:</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>erp.thornfieldlsm.com — Customer master filtered on account_origin = "Thornfield native"</t>
         </is>
       </c>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
-      <c r="G10" s="22" t="n"/>
+      <c r="C10" s="49" t="n"/>
+      <c r="D10" s="49" t="n"/>
+      <c r="E10" s="49" t="n"/>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="50" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
@@ -999,16 +1209,16 @@
           <t>Related methodology:</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>See Finance's FY2025 proration methodology for the combined-entity reporting convention that consumes these standalone figures.</t>
         </is>
       </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="24" t="n"/>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="25" t="n"/>
+      <c r="C11" s="51" t="n"/>
+      <c r="D11" s="51" t="n"/>
+      <c r="E11" s="51" t="n"/>
+      <c r="F11" s="51" t="n"/>
+      <c r="G11" s="52" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1"/>
     <row r="13" ht="32" customHeight="1">
@@ -1645,7 +1855,7 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="28" t="inlineStr">
         <is>
-          <t>CUST-2025-0134</t>
+          <t>CUST-2025-0296</t>
         </is>
       </c>
       <c r="B36" s="29" t="inlineStr">
@@ -1915,7 +2125,7 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="28" t="inlineStr">
         <is>
-          <t>CUST-2025-0189</t>
+          <t>CUST-2025-0297</t>
         </is>
       </c>
       <c r="B46" s="29" t="inlineStr">
@@ -2297,119 +2507,119 @@
           <t>FY2025 Total:</t>
         </is>
       </c>
-      <c r="B61" s="38" t="n"/>
-      <c r="C61" s="38" t="n"/>
-      <c r="D61" s="38" t="n"/>
-      <c r="E61" s="38" t="n"/>
-      <c r="F61" s="38" t="n"/>
+      <c r="B61" s="53" t="n"/>
+      <c r="C61" s="53" t="n"/>
+      <c r="D61" s="53" t="n"/>
+      <c r="E61" s="53" t="n"/>
+      <c r="F61" s="54" t="n"/>
       <c r="G61" s="39" t="n">
         <v>6004500</v>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1"/>
     <row r="63" ht="26" customHeight="1">
-      <c r="A63" s="40" t="inlineStr">
+      <c r="A63" s="57" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B63" s="41" t="n"/>
-      <c r="C63" s="41" t="n"/>
-      <c r="D63" s="41" t="n"/>
-      <c r="E63" s="41" t="n"/>
-      <c r="F63" s="41" t="n"/>
-      <c r="G63" s="41" t="n"/>
+      <c r="B63" s="55" t="n"/>
+      <c r="C63" s="55" t="n"/>
+      <c r="D63" s="55" t="n"/>
+      <c r="E63" s="55" t="n"/>
+      <c r="F63" s="55" t="n"/>
+      <c r="G63" s="55" t="n"/>
     </row>
     <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="42" t="inlineStr">
+      <c r="A64" s="58" t="inlineStr">
         <is>
           <t>•  Tab owner (per document-control convention): Ted Kowalczyk (TF-0018), VP Paid Media. Finance-compiled; management sign-off retained on file. Not for external distribution.</t>
         </is>
       </c>
-      <c r="B64" s="42" t="n"/>
-      <c r="C64" s="42" t="n"/>
-      <c r="D64" s="42" t="n"/>
-      <c r="E64" s="42" t="n"/>
-      <c r="F64" s="42" t="n"/>
-      <c r="G64" s="42" t="n"/>
+      <c r="B64" s="56" t="n"/>
+      <c r="C64" s="56" t="n"/>
+      <c r="D64" s="56" t="n"/>
+      <c r="E64" s="56" t="n"/>
+      <c r="F64" s="56" t="n"/>
+      <c r="G64" s="56" t="n"/>
     </row>
     <row r="65" ht="48" customHeight="1">
-      <c r="A65" s="42" t="inlineStr">
+      <c r="A65" s="58" t="inlineStr">
         <is>
           <t>•  Client roster is 45 Thornfield-native accounts active at any point during FY2025 (active_clients_pre_acquisition per HR/Ops headcount reconciliation). Accounts inherited from Bramwell Scientific Marketing on the 09/01/2025 close date are reported separately in the Bramwell FY2025 Standalone workbook and are not summed here.</t>
         </is>
       </c>
-      <c r="B65" s="42" t="n"/>
-      <c r="C65" s="42" t="n"/>
-      <c r="D65" s="42" t="n"/>
-      <c r="E65" s="42" t="n"/>
-      <c r="F65" s="42" t="n"/>
-      <c r="G65" s="42" t="n"/>
+      <c r="B65" s="56" t="n"/>
+      <c r="C65" s="56" t="n"/>
+      <c r="D65" s="56" t="n"/>
+      <c r="E65" s="56" t="n"/>
+      <c r="F65" s="56" t="n"/>
+      <c r="G65" s="56" t="n"/>
     </row>
     <row r="66" ht="40" customHeight="1">
-      <c r="A66" s="42" t="inlineStr">
+      <c r="A66" s="58" t="inlineStr">
         <is>
           <t>•  Revenue is booked on the Thornfield ERPNext instance (Frappe/ERPNext v14, erp.thornfieldlsm.com) from the Sales Invoice ledger; figures reflect invoiced service fees and retainers only. Managed platform spend passed through to media vendors is excluded.</t>
         </is>
       </c>
-      <c r="B66" s="42" t="n"/>
-      <c r="C66" s="42" t="n"/>
-      <c r="D66" s="42" t="n"/>
-      <c r="E66" s="42" t="n"/>
-      <c r="F66" s="42" t="n"/>
-      <c r="G66" s="42" t="n"/>
+      <c r="B66" s="56" t="n"/>
+      <c r="C66" s="56" t="n"/>
+      <c r="D66" s="56" t="n"/>
+      <c r="E66" s="56" t="n"/>
+      <c r="F66" s="56" t="n"/>
+      <c r="G66" s="56" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="42" t="inlineStr">
+      <c r="A67" s="58" t="inlineStr">
         <is>
           <t>•  Quarterly columns aggregate Sales Invoice postings by invoice date within each calendar quarter of FY2025. Row totals are the sum of Q1–Q4; the column total row is the sum down each quarter.</t>
         </is>
       </c>
-      <c r="B67" s="42" t="n"/>
-      <c r="C67" s="42" t="n"/>
-      <c r="D67" s="42" t="n"/>
-      <c r="E67" s="42" t="n"/>
-      <c r="F67" s="42" t="n"/>
-      <c r="G67" s="42" t="n"/>
+      <c r="B67" s="56" t="n"/>
+      <c r="C67" s="56" t="n"/>
+      <c r="D67" s="56" t="n"/>
+      <c r="E67" s="56" t="n"/>
+      <c r="F67" s="56" t="n"/>
+      <c r="G67" s="56" t="n"/>
     </row>
     <row r="68" ht="36" customHeight="1">
-      <c r="A68" s="42" t="inlineStr">
+      <c r="A68" s="58" t="inlineStr">
         <is>
           <t>•  Marlstone Bioscience (CUST-2025-0033) Q4 reflects the raw Sales Invoice figure ($187,400) pre-adjustment; credit memo CM-2025-0088 ($4,500) is applied downstream in the Q4 reconciliation workpaper and does not appear in this standalone.</t>
         </is>
       </c>
-      <c r="B68" s="42" t="n"/>
-      <c r="C68" s="42" t="n"/>
-      <c r="D68" s="42" t="n"/>
-      <c r="E68" s="42" t="n"/>
-      <c r="F68" s="42" t="n"/>
-      <c r="G68" s="42" t="n"/>
+      <c r="B68" s="56" t="n"/>
+      <c r="C68" s="56" t="n"/>
+      <c r="D68" s="56" t="n"/>
+      <c r="E68" s="56" t="n"/>
+      <c r="F68" s="56" t="n"/>
+      <c r="G68" s="56" t="n"/>
     </row>
     <row r="69" ht="48" customHeight="1">
-      <c r="A69" s="42" t="inlineStr">
+      <c r="A69" s="58" t="inlineStr">
         <is>
           <t>•  Caldwell Diagnostics (CUST-2025-0088) Q4 standalone revenue ($32,100) excludes $13,980 of pass-through platform spend billed at cost within the fixed monthly retainer; the Q4 billing export ($46,080 = 3 × $15,360 MSA retainer) captures the gross retainer amount. Bridge: $32,100 service fee + $13,980 pass-through platform = $46,080.</t>
         </is>
       </c>
-      <c r="B69" s="42" t="n"/>
-      <c r="C69" s="42" t="n"/>
-      <c r="D69" s="42" t="n"/>
-      <c r="E69" s="42" t="n"/>
-      <c r="F69" s="42" t="n"/>
-      <c r="G69" s="42" t="n"/>
+      <c r="B69" s="56" t="n"/>
+      <c r="C69" s="56" t="n"/>
+      <c r="D69" s="56" t="n"/>
+      <c r="E69" s="56" t="n"/>
+      <c r="F69" s="56" t="n"/>
+      <c r="G69" s="56" t="n"/>
     </row>
     <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="42" t="inlineStr">
+      <c r="A70" s="58" t="inlineStr">
         <is>
           <t>•  Wrenfield Scientific (CUST-2025-0201) Q4 standalone reflects the post-credit-memo reconciled service-fee figure; the raw billing export shows the pre-credit-memo total.</t>
         </is>
       </c>
-      <c r="B70" s="42" t="n"/>
-      <c r="C70" s="42" t="n"/>
-      <c r="D70" s="42" t="n"/>
-      <c r="E70" s="42" t="n"/>
-      <c r="F70" s="42" t="n"/>
-      <c r="G70" s="42" t="n"/>
+      <c r="B70" s="56" t="n"/>
+      <c r="C70" s="56" t="n"/>
+      <c r="D70" s="56" t="n"/>
+      <c r="E70" s="56" t="n"/>
+      <c r="F70" s="56" t="n"/>
+      <c r="G70" s="56" t="n"/>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="43" t="inlineStr">
@@ -2425,17 +2635,17 @@
       <c r="G71" s="43" t="n"/>
     </row>
     <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="42" t="inlineStr">
+      <c r="A72" s="58" t="inlineStr">
         <is>
           <t>•  Feeds into the FY2025 combined-entity headline figure per Finance's FY2025 proration methodology.</t>
         </is>
       </c>
-      <c r="B72" s="42" t="n"/>
-      <c r="C72" s="42" t="n"/>
-      <c r="D72" s="42" t="n"/>
-      <c r="E72" s="42" t="n"/>
-      <c r="F72" s="42" t="n"/>
-      <c r="G72" s="42" t="n"/>
+      <c r="B72" s="56" t="n"/>
+      <c r="C72" s="56" t="n"/>
+      <c r="D72" s="56" t="n"/>
+      <c r="E72" s="56" t="n"/>
+      <c r="F72" s="56" t="n"/>
+      <c r="G72" s="56" t="n"/>
     </row>
     <row r="73" ht="16" customHeight="1"/>
     <row r="74" ht="20" customHeight="1">
@@ -2444,12 +2654,6 @@
           <t>Ted Kowalczyk</t>
         </is>
       </c>
-      <c r="B74" s="44" t="n"/>
-      <c r="C74" s="44" t="n"/>
-      <c r="D74" s="44" t="n"/>
-      <c r="E74" s="44" t="n"/>
-      <c r="F74" s="44" t="n"/>
-      <c r="G74" s="44" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="45" t="inlineStr">

--- a/filesystem/Finance/Financials/Thornfield_FY2025_standalone.xlsx
+++ b/filesystem/Finance/Financials/Thornfield_FY2025_standalone.xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2609,78 +2609,66 @@
       <c r="G69" s="56" t="n"/>
     </row>
     <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="58" t="inlineStr">
-        <is>
-          <t>•  Wrenfield Scientific (CUST-2025-0201) Q4 standalone reflects the post-credit-memo reconciled service-fee figure; the raw billing export shows the pre-credit-memo total.</t>
-        </is>
-      </c>
-      <c r="B70" s="56" t="n"/>
-      <c r="C70" s="56" t="n"/>
-      <c r="D70" s="56" t="n"/>
-      <c r="E70" s="56" t="n"/>
-      <c r="F70" s="56" t="n"/>
-      <c r="G70" s="56" t="n"/>
+      <c r="A70" s="43" t="inlineStr">
+        <is>
+          <t>•  Per capita: $6,000,000 ÷ 54 FTEs = ~$111K revenue per employee (Thornfield pre-acquisition headcount).</t>
+        </is>
+      </c>
+      <c r="B70" s="43" t="n"/>
+      <c r="C70" s="43" t="n"/>
+      <c r="D70" s="43" t="n"/>
+      <c r="E70" s="43" t="n"/>
+      <c r="F70" s="43" t="n"/>
+      <c r="G70" s="43" t="n"/>
     </row>
     <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="43" t="inlineStr">
-        <is>
-          <t>•  Per capita: $6,000,000 ÷ 54 FTEs = ~$111K revenue per employee (Thornfield pre-acquisition headcount).</t>
-        </is>
-      </c>
-      <c r="B71" s="43" t="n"/>
-      <c r="C71" s="43" t="n"/>
-      <c r="D71" s="43" t="n"/>
-      <c r="E71" s="43" t="n"/>
-      <c r="F71" s="43" t="n"/>
-      <c r="G71" s="43" t="n"/>
-    </row>
-    <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="58" t="inlineStr">
+      <c r="A71" s="58" t="inlineStr">
         <is>
           <t>•  Feeds into the FY2025 combined-entity headline figure per Finance's FY2025 proration methodology.</t>
         </is>
       </c>
-      <c r="B72" s="56" t="n"/>
-      <c r="C72" s="56" t="n"/>
-      <c r="D72" s="56" t="n"/>
-      <c r="E72" s="56" t="n"/>
-      <c r="F72" s="56" t="n"/>
-      <c r="G72" s="56" t="n"/>
-    </row>
-    <row r="73" ht="16" customHeight="1"/>
+      <c r="B71" s="56" t="n"/>
+      <c r="C71" s="56" t="n"/>
+      <c r="D71" s="56" t="n"/>
+      <c r="E71" s="56" t="n"/>
+      <c r="F71" s="56" t="n"/>
+      <c r="G71" s="56" t="n"/>
+    </row>
+    <row r="72" ht="24" customHeight="1"/>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="44" t="inlineStr">
+        <is>
+          <t>Ted Kowalczyk</t>
+        </is>
+      </c>
+    </row>
     <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="44" t="inlineStr">
-        <is>
-          <t>Ted Kowalczyk</t>
-        </is>
-      </c>
+      <c r="A74" s="45" t="inlineStr">
+        <is>
+          <t>VP, Paid Media — Thornfield Life Sciences Marketing, Inc.</t>
+        </is>
+      </c>
+      <c r="B74" s="45" t="n"/>
+      <c r="C74" s="45" t="n"/>
+      <c r="D74" s="45" t="n"/>
+      <c r="E74" s="45" t="n"/>
+      <c r="F74" s="45" t="n"/>
+      <c r="G74" s="45" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="45" t="inlineStr">
-        <is>
-          <t>VP, Paid Media — Thornfield Life Sciences Marketing, Inc.</t>
-        </is>
-      </c>
-      <c r="B75" s="45" t="n"/>
-      <c r="C75" s="45" t="n"/>
-      <c r="D75" s="45" t="n"/>
-      <c r="E75" s="45" t="n"/>
-      <c r="F75" s="45" t="n"/>
-      <c r="G75" s="45" t="n"/>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="46" t="inlineStr">
+      <c r="A75" s="46" t="inlineStr">
         <is>
           <t>Filed to /Finance/Financials/ — FY2025 close pack</t>
         </is>
       </c>
-      <c r="B76" s="46" t="n"/>
-      <c r="C76" s="46" t="n"/>
-      <c r="D76" s="46" t="n"/>
-      <c r="E76" s="46" t="n"/>
-      <c r="F76" s="46" t="n"/>
-      <c r="G76" s="46" t="n"/>
-    </row>
+      <c r="B75" s="46" t="n"/>
+      <c r="C75" s="46" t="n"/>
+      <c r="D75" s="46" t="n"/>
+      <c r="E75" s="46" t="n"/>
+      <c r="F75" s="46" t="n"/>
+      <c r="G75" s="46" t="n"/>
+    </row>
+    <row r="76" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="B8:G8"/>

--- a/filesystem/Finance/Financials/Thornfield_FY2025_standalone.xlsx
+++ b/filesystem/Finance/Financials/Thornfield_FY2025_standalone.xlsx
@@ -1411,10 +1411,10 @@
         <v>36700</v>
       </c>
       <c r="E19" s="34" t="n">
-        <v>38100</v>
+        <v>50750</v>
       </c>
       <c r="F19" s="34" t="n">
-        <v>39600</v>
+        <v>26950</v>
       </c>
       <c r="G19" s="31" t="n">
         <v>146700</v>
@@ -1762,10 +1762,10 @@
         <v>78100</v>
       </c>
       <c r="E32" s="30" t="n">
-        <v>81200</v>
+        <v>114200</v>
       </c>
       <c r="F32" s="30" t="n">
-        <v>84400</v>
+        <v>51400</v>
       </c>
       <c r="G32" s="31" t="n">
         <v>312400</v>
@@ -1924,10 +1924,10 @@
         <v>16200</v>
       </c>
       <c r="E38" s="30" t="n">
-        <v>16900</v>
+        <v>20000</v>
       </c>
       <c r="F38" s="30" t="n">
-        <v>17500</v>
+        <v>14400</v>
       </c>
       <c r="G38" s="31" t="n">
         <v>64900</v>
@@ -2113,10 +2113,10 @@
         <v>22100</v>
       </c>
       <c r="E45" s="34" t="n">
-        <v>23000</v>
+        <v>28800</v>
       </c>
       <c r="F45" s="34" t="n">
-        <v>23800</v>
+        <v>18000</v>
       </c>
       <c r="G45" s="31" t="n">
         <v>88300</v>
@@ -2248,10 +2248,10 @@
         <v>42100</v>
       </c>
       <c r="E50" s="30" t="n">
-        <v>43700</v>
+        <v>64000</v>
       </c>
       <c r="F50" s="30" t="n">
-        <v>45400</v>
+        <v>25100</v>
       </c>
       <c r="G50" s="31" t="n">
         <v>168200</v>
@@ -2614,12 +2614,12 @@
           <t>•  Per capita: $6,000,000 ÷ 54 FTEs = ~$111K revenue per employee (Thornfield pre-acquisition headcount).</t>
         </is>
       </c>
-      <c r="B70" s="43" t="n"/>
-      <c r="C70" s="43" t="n"/>
-      <c r="D70" s="43" t="n"/>
-      <c r="E70" s="43" t="n"/>
-      <c r="F70" s="43" t="n"/>
-      <c r="G70" s="43" t="n"/>
+      <c r="B70" s="56" t="n"/>
+      <c r="C70" s="56" t="n"/>
+      <c r="D70" s="56" t="n"/>
+      <c r="E70" s="56" t="n"/>
+      <c r="F70" s="56" t="n"/>
+      <c r="G70" s="56" t="n"/>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="58" t="inlineStr">
@@ -2648,12 +2648,6 @@
           <t>VP, Paid Media — Thornfield Life Sciences Marketing, Inc.</t>
         </is>
       </c>
-      <c r="B74" s="45" t="n"/>
-      <c r="C74" s="45" t="n"/>
-      <c r="D74" s="45" t="n"/>
-      <c r="E74" s="45" t="n"/>
-      <c r="F74" s="45" t="n"/>
-      <c r="G74" s="45" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="46" t="inlineStr">

--- a/filesystem/Finance/Financials/Thornfield_FY2025_standalone.xlsx
+++ b/filesystem/Finance/Financials/Thornfield_FY2025_standalone.xlsx
@@ -590,7 +590,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -739,6 +739,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2484,19 +2487,24 @@
           <t>Thornfield FY2025 Standalone</t>
         </is>
       </c>
-      <c r="C59" s="36" t="n">
+      <c r="C59" s="36">
+        <f>SUM(C14:C58)</f>
         <v>1309700</v>
       </c>
-      <c r="D59" s="36" t="n">
+      <c r="D59" s="36">
+        <f>SUM(D14:D58)</f>
         <v>1480600</v>
       </c>
-      <c r="E59" s="36" t="n">
-        <v>1542100</v>
-      </c>
-      <c r="F59" s="36" t="n">
-        <v>1672100</v>
-      </c>
-      <c r="G59" s="36" t="n">
+      <c r="E59" s="36">
+        <f>SUM(E14:E58)</f>
+        <v>1616950</v>
+      </c>
+      <c r="F59" s="36">
+        <f>SUM(F14:F58)</f>
+        <v>1597250</v>
+      </c>
+      <c r="G59" s="36">
+        <f>SUM(C59:F59)</f>
         <v>6004500</v>
       </c>
     </row>
@@ -2512,7 +2520,8 @@
       <c r="D61" s="53" t="n"/>
       <c r="E61" s="53" t="n"/>
       <c r="F61" s="54" t="n"/>
-      <c r="G61" s="39" t="n">
+      <c r="G61" s="39">
+        <f>G59</f>
         <v>6004500</v>
       </c>
     </row>
@@ -2609,7 +2618,7 @@
       <c r="G69" s="56" t="n"/>
     </row>
     <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="43" t="inlineStr">
+      <c r="A70" s="59" t="inlineStr">
         <is>
           <t>•  Per capita: $6,000,000 ÷ 54 FTEs = ~$111K revenue per employee (Thornfield pre-acquisition headcount).</t>
         </is>
@@ -2621,7 +2630,7 @@
       <c r="F70" s="56" t="n"/>
       <c r="G70" s="56" t="n"/>
     </row>
-    <row r="71" ht="24" customHeight="1">
+    <row r="71" ht="16" customHeight="1">
       <c r="A71" s="58" t="inlineStr">
         <is>
           <t>•  Feeds into the FY2025 combined-entity headline figure per Finance's FY2025 proration methodology.</t>
@@ -2664,7 +2673,7 @@
     </row>
     <row r="76" ht="18" customHeight="1"/>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
     <mergeCell ref="B8:G8"/>
     <mergeCell ref="A72:G72"/>
     <mergeCell ref="A68:G68"/>
@@ -2686,6 +2695,7 @@
     <mergeCell ref="A66:G66"/>
     <mergeCell ref="A74:G74"/>
     <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A71:G71"/>
     <mergeCell ref="B11:G11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>

--- a/filesystem/Finance/Financials/Thornfield_FY2025_standalone.xlsx
+++ b/filesystem/Finance/Financials/Thornfield_FY2025_standalone.xlsx
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>Meridian Biosystems</t>
+          <t>Thistlewood Biosystems</t>
         </is>
       </c>
       <c r="C14" s="30" t="n">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B40" s="29" t="inlineStr">
         <is>
-          <t>Meridian Cell Lines</t>
+          <t>Cranmere Cell Lines</t>
         </is>
       </c>
       <c r="C40" s="30" t="n">

--- a/filesystem/Finance/Financials/Thornfield_FY2025_standalone.xlsx
+++ b/filesystem/Finance/Financials/Thornfield_FY2025_standalone.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -148,6 +148,11 @@
       <color rgb="0064748B"/>
       <sz val="8.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF475569"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -590,7 +595,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -742,6 +747,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2659,7 +2667,7 @@
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="46" t="inlineStr">
+      <c r="A75" s="60" t="inlineStr">
         <is>
           <t>Filed to /Finance/Financials/ — FY2025 close pack</t>
         </is>
